--- a/Cerinte_functionale(1).xlsx
+++ b/Cerinte_functionale(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\serba\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2305B44C-1206-454F-A0D8-D8647765D6FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677B7075-27F5-43A3-A1C9-81AAF3DEF234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>Caz de utilizare</t>
   </si>
@@ -49,75 +49,42 @@
     <t>REQ-2</t>
   </si>
   <si>
-    <t>Sistemul trebuie sa-i furnizeze angajatului juridic informatii filtrate in functie de tipul de contract ales</t>
-  </si>
-  <si>
     <t>NFR-1</t>
   </si>
   <si>
     <t>Sistemul trebuie sa proceseze cererea intr-un timp de maxim 1s, si sa aiba disponibilitate in 97% din timpul programului de lucru</t>
   </si>
   <si>
-    <t>REQ-3</t>
-  </si>
-  <si>
     <t>Sistemul trebuie sa permita angajatului juridic sa faca completari si modificari ale contractului</t>
   </si>
   <si>
-    <t>REQ-4</t>
-  </si>
-  <si>
     <t>Sistemul trebuie sa adauge contractul in arhiva</t>
   </si>
   <si>
     <t>Definire acte de voiaj</t>
   </si>
   <si>
-    <t>REQ-5</t>
-  </si>
-  <si>
     <t>Sistemul trebuie sa afiseze angajatului juridic listele de angajati si atributele juridice ale acestora</t>
   </si>
   <si>
-    <t>REQ-6</t>
-  </si>
-  <si>
     <t>Sistemul trebuie sa ii permita angajatului juridic selectarea angajatului pentru care se defineste actul de voiaj</t>
   </si>
   <si>
-    <t>REQ-7</t>
-  </si>
-  <si>
     <t>Sistemul trebuie sa returneze tipurile de acte care vizeaza activitatile angajatului selectat</t>
   </si>
   <si>
-    <t>REQ-8</t>
-  </si>
-  <si>
     <t>Sistemul trebuie sa ii permita angajatului juridic selectarea actului dorit</t>
   </si>
   <si>
-    <t>REQ-9</t>
-  </si>
-  <si>
     <t>Sistemul trebuie sa furnizeze dosarul de voiaj al angajatului selectat</t>
   </si>
   <si>
-    <t>REQ-10</t>
-  </si>
-  <si>
     <t>Sistemul trebuie sa completeze automat datele necesare pentru actele selectate</t>
   </si>
   <si>
-    <t>REQ-11</t>
-  </si>
-  <si>
     <t>Sistemul trebuie sa permita angajatului juridic sa verifice documentul si sa faca actualizari, in cazul in care este incomplet</t>
   </si>
   <si>
-    <t>REQ-12</t>
-  </si>
-  <si>
     <t>Sistemul trebuie sa adauge dosarul de voiaj actualizat in arhiva</t>
   </si>
   <si>
@@ -125,6 +92,51 @@
   </si>
   <si>
     <t>NFR-2</t>
+  </si>
+  <si>
+    <t>Sistemul trebuie sa permita angajatului juridic sa defineasca contracte</t>
+  </si>
+  <si>
+    <t>REQ-1.1</t>
+  </si>
+  <si>
+    <t>REQ-1.2</t>
+  </si>
+  <si>
+    <t>REQ-1.2.1</t>
+  </si>
+  <si>
+    <t>REQ-1.3</t>
+  </si>
+  <si>
+    <t>REQ-1.4</t>
+  </si>
+  <si>
+    <t>Sistemul trebuie sa permita angajatului juridic sa defineasca actele de voiaj ale angajatilor</t>
+  </si>
+  <si>
+    <t>REQ-2.1.1</t>
+  </si>
+  <si>
+    <t>REQ-2.2</t>
+  </si>
+  <si>
+    <t>REQ-2.2.1</t>
+  </si>
+  <si>
+    <t>REQ-2.2.1.1</t>
+  </si>
+  <si>
+    <t>Sistemul trebuie sa-i furnizeze angajatului juridic informatii</t>
+  </si>
+  <si>
+    <t>REQ-2.3</t>
+  </si>
+  <si>
+    <t>REQ-2.3.1</t>
+  </si>
+  <si>
+    <t>REQ-2.4</t>
   </si>
 </sst>
 </file>
@@ -160,8 +172,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -464,151 +485,193 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.81640625" customWidth="1"/>
     <col min="2" max="2" width="18.08984375" customWidth="1"/>
+    <col min="3" max="3" width="109.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+      <c r="B2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B3" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="2"/>
+      <c r="B4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+      <c r="B5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="2"/>
+      <c r="B6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="2"/>
+      <c r="B7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="2"/>
+      <c r="B8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B9" s="3"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="2"/>
+      <c r="B11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="2"/>
+      <c r="B12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="C12" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="2"/>
+      <c r="B13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" t="s">
         <v>16</v>
       </c>
-      <c r="B8" t="s">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="2"/>
+      <c r="B14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
         <v>17</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="2"/>
+      <c r="B15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B9" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="2"/>
+      <c r="B16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" t="s">
         <v>19</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="2"/>
+      <c r="B17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B10" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="2"/>
+      <c r="B18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" t="s">
         <v>21</v>
       </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="2"/>
+      <c r="B19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" t="s">
-        <v>33</v>
-      </c>
-    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="A10:A19"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Cerinte_functionale(1).xlsx
+++ b/Cerinte_functionale(1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\serba\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677B7075-27F5-43A3-A1C9-81AAF3DEF234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDC0D50-D090-4EC2-999D-640E8B7BAE41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>Caz de utilizare</t>
   </si>
@@ -55,6 +55,9 @@
     <t>Sistemul trebuie sa proceseze cererea intr-un timp de maxim 1s, si sa aiba disponibilitate in 97% din timpul programului de lucru</t>
   </si>
   <si>
+    <t>REQ-3</t>
+  </si>
+  <si>
     <t>Sistemul trebuie sa permita angajatului juridic sa faca completari si modificari ale contractului</t>
   </si>
   <si>
@@ -137,6 +140,42 @@
   </si>
   <si>
     <t>REQ-2.4</t>
+  </si>
+  <si>
+    <t>Gestiunea departamentelor</t>
+  </si>
+  <si>
+    <t>Sistemul trebuie sa-i permita administratorului sa gestioneze fiecare departament si angajat</t>
+  </si>
+  <si>
+    <t>Sistemul trebuie sa-i permita administratorului sa vizualizeze fiecare departament si detalii despre aceasta</t>
+  </si>
+  <si>
+    <t>Sistemul trebuie sa-i permita administratorului sa selecteze departamentul dorit</t>
+  </si>
+  <si>
+    <t>Sistemul trebuie sa-i afiseze administratorului actiunile pe care le poate face in cadrul departamentelor</t>
+  </si>
+  <si>
+    <t>Sistemul trebuie sa-i permita administratorului sa adauge sau sa stearga un departament</t>
+  </si>
+  <si>
+    <t>Sistemul trebuie sa-i permita administratorului sa adauge angajati in departament</t>
+  </si>
+  <si>
+    <t>Sistemul trebuie sa-i permita administratorului sa adauge angajati intr-o echipa</t>
+  </si>
+  <si>
+    <t>Sistemul trebuie sa-i permita administratorului sa elimine angajati din departament</t>
+  </si>
+  <si>
+    <t>Sistemul trebuie sa-i permita administratorului sa elimine angajati dintr-o echipa</t>
+  </si>
+  <si>
+    <t>Sistemul trebuie sa-i permita administratorului sa adauge instrumente software in departament</t>
+  </si>
+  <si>
+    <t>Sistemul trebuie sa-i permita administratorului sa elimine instrumente software din departament</t>
   </si>
 </sst>
 </file>
@@ -485,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.81640625" customWidth="1"/>
@@ -512,7 +551,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" s="1"/>
     </row>
@@ -521,7 +560,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -530,7 +569,7 @@
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
       <c r="B4" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
@@ -539,10 +578,10 @@
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
       <c r="B5" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -557,19 +596,19 @@
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="2"/>
       <c r="B7" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="2"/>
       <c r="B8" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -577,22 +616,22 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
       <c r="B11" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -601,70 +640,131 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="2"/>
       <c r="B13" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
       <c r="B14" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
       <c r="B15" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="2"/>
       <c r="B16" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="2"/>
       <c r="B17" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="2"/>
       <c r="B18" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="2"/>
       <c r="B19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
         <v>23</v>
       </c>
-      <c r="C19" t="s">
-        <v>22</v>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C23" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C24" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C27" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C28" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C29" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C30" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C31" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/Cerinte_functionale(1).xlsx
+++ b/Cerinte_functionale(1).xlsx
@@ -1,26 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\serba\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDC0D50-D090-4EC2-999D-640E8B7BAE41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F279973C-48E1-41D5-9D54-0A04C6447E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cerinte" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="86">
   <si>
     <t>Caz de utilizare</t>
   </si>
@@ -176,16 +190,139 @@
   </si>
   <si>
     <t>Sistemul trebuie sa-i permita administratorului sa elimine instrumente software din departament</t>
+  </si>
+  <si>
+    <t>Interfata</t>
+  </si>
+  <si>
+    <t>Tehnologia aleasa</t>
+  </si>
+  <si>
+    <t>Metoda de verificare</t>
+  </si>
+  <si>
+    <t>Interfata pt definire contracte</t>
+  </si>
+  <si>
+    <t>Interfata vizualizare rapoarte</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Aplicatie desktop</t>
+  </si>
+  <si>
+    <t>validare selectie</t>
+  </si>
+  <si>
+    <t>Sistemul trebuie sa-i furnizeze angajatului juridic informatii filtrate in functie de tipul de contract ales</t>
+  </si>
+  <si>
+    <t>lista dropdown</t>
+  </si>
+  <si>
+    <t>formular</t>
+  </si>
+  <si>
+    <t>PostgreSQL</t>
+  </si>
+  <si>
+    <t>Test de performanta</t>
+  </si>
+  <si>
+    <t>Test de replicare</t>
+  </si>
+  <si>
+    <t>Test functional</t>
+  </si>
+  <si>
+    <t>Interfata pt definire acte de voiaj</t>
+  </si>
+  <si>
+    <t>Test de integrare</t>
+  </si>
+  <si>
+    <t>preluare informatii din aplicatia dedicata</t>
+  </si>
+  <si>
+    <t>preluare tipuri de acte din aplicatia dedicata</t>
+  </si>
+  <si>
+    <t>preluare act din arhiva</t>
+  </si>
+  <si>
+    <t>completare automata acte</t>
+  </si>
+  <si>
+    <t>Aplicatie desktop .NET</t>
+  </si>
+  <si>
+    <t>Interfata pt definire contracte/lista dropdown</t>
+  </si>
+  <si>
+    <t>REQ-1.1.1</t>
+  </si>
+  <si>
+    <t>REQ-3.1</t>
+  </si>
+  <si>
+    <t>REQ-3.1.1</t>
+  </si>
+  <si>
+    <t>REQ-3.2</t>
+  </si>
+  <si>
+    <t>REQ-3.3</t>
+  </si>
+  <si>
+    <t>REQ-3.4</t>
+  </si>
+  <si>
+    <t>REQ-3.5</t>
+  </si>
+  <si>
+    <t>REQ-3.6</t>
+  </si>
+  <si>
+    <t>REQ-3.7</t>
+  </si>
+  <si>
+    <t>REQ-3.8</t>
+  </si>
+  <si>
+    <t>REQ-3.9</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="6" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -211,7 +348,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -219,6 +356,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -524,13 +666,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.81640625" customWidth="1"/>
     <col min="2" max="2" width="18.08984375" customWidth="1"/>
     <col min="3" max="3" width="109.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="4" max="4" width="17.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -547,7 +689,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C2" t="s">
@@ -556,10 +698,10 @@
       <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C3" t="s">
@@ -567,8 +709,8 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="6"/>
+      <c r="B4" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C4" t="s">
@@ -576,8 +718,8 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="6"/>
+      <c r="B5" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C5" t="s">
@@ -585,8 +727,8 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="2"/>
-      <c r="B6" s="3" t="s">
+      <c r="A6" s="6"/>
+      <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
@@ -594,8 +736,8 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="2"/>
-      <c r="B7" s="3" t="s">
+      <c r="A7" s="6"/>
+      <c r="B7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C7" t="s">
@@ -603,8 +745,8 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3" t="s">
+      <c r="A8" s="6"/>
+      <c r="B8" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C8" t="s">
@@ -612,13 +754,13 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B9" s="3"/>
+      <c r="B9" s="2"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C10" t="s">
@@ -626,8 +768,8 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3" t="s">
+      <c r="A11" s="6"/>
+      <c r="B11" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C11" t="s">
@@ -635,8 +777,8 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3" t="s">
+      <c r="A12" s="6"/>
+      <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C12" t="s">
@@ -644,8 +786,8 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3" t="s">
+      <c r="A13" s="6"/>
+      <c r="B13" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C13" t="s">
@@ -653,8 +795,8 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="2"/>
-      <c r="B14" s="3" t="s">
+      <c r="A14" s="6"/>
+      <c r="B14" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C14" t="s">
@@ -662,8 +804,8 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="2"/>
-      <c r="B15" s="3" t="s">
+      <c r="A15" s="6"/>
+      <c r="B15" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C15" t="s">
@@ -671,8 +813,8 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="2"/>
-      <c r="B16" s="3" t="s">
+      <c r="A16" s="6"/>
+      <c r="B16" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C16" t="s">
@@ -680,8 +822,8 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="2"/>
-      <c r="B17" s="3" t="s">
+      <c r="A17" s="6"/>
+      <c r="B17" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C17" t="s">
@@ -689,8 +831,8 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3" t="s">
+      <c r="A18" s="6"/>
+      <c r="B18" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C18" t="s">
@@ -698,8 +840,8 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="2"/>
-      <c r="B19" s="3" t="s">
+      <c r="A19" s="6"/>
+      <c r="B19" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C19" t="s">
@@ -707,10 +849,10 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
+      <c r="A21" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C21" t="s">
@@ -718,60 +860,528 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="6"/>
       <c r="C22" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="6"/>
       <c r="C23" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="6"/>
       <c r="C24" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="6"/>
       <c r="C25" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="6"/>
       <c r="C26" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="6"/>
       <c r="C27" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="6"/>
       <c r="C28" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="6"/>
       <c r="C29" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="6"/>
       <c r="C30" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="6"/>
       <c r="C31" t="s">
         <v>51</v>
       </c>
     </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C33" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A3:A8"/>
     <mergeCell ref="A10:A19"/>
+    <mergeCell ref="A21:A31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A3E8EB5-E554-43E7-A345-50116AF6816A}">
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="24.08984375" customWidth="1"/>
+    <col min="2" max="2" width="12.08984375" customWidth="1"/>
+    <col min="3" max="3" width="105" customWidth="1"/>
+    <col min="4" max="4" width="28.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="6"/>
+      <c r="B4" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="6"/>
+      <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="6"/>
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="6"/>
+      <c r="B7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="6"/>
+      <c r="B8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="6"/>
+      <c r="B11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="6"/>
+      <c r="B12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="6"/>
+      <c r="B13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="6"/>
+      <c r="B14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="6"/>
+      <c r="B15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" t="s">
+        <v>71</v>
+      </c>
+      <c r="F15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="6"/>
+      <c r="B16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="6"/>
+      <c r="B17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="6"/>
+      <c r="B18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="6"/>
+      <c r="B19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" t="s">
+        <v>57</v>
+      </c>
+      <c r="F19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="6"/>
+      <c r="B22" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="6"/>
+      <c r="B23" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="6"/>
+      <c r="B24" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="6"/>
+      <c r="B25" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="6"/>
+      <c r="B26" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="6"/>
+      <c r="B27" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="6"/>
+      <c r="B28" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C28" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="6"/>
+      <c r="B29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="6"/>
+      <c r="B30" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="6"/>
+      <c r="B31" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" t="s">
+        <v>51</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="A10:A19"/>
+    <mergeCell ref="A21:A31"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>